--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104708_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104708_W28.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8275</v>
+        <v>5.1712</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0016</v>
+        <v>4.3744</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8259</v>
+        <v>0.7968</v>
       </c>
       <c r="G2" t="n">
-        <v>4.664</v>
+        <v>4.6692</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4329</v>
+        <v>2.4299</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2311</v>
+        <v>2.2393</v>
       </c>
       <c r="J2" t="n">
-        <v>5.3928</v>
+        <v>5.3712</v>
       </c>
       <c r="K2" t="n">
-        <v>4.0867</v>
+        <v>4.0679</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3061</v>
+        <v>1.3033</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7289</v>
+        <v>-0.702</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6539</v>
+        <v>-1.638</v>
       </c>
       <c r="O2" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1294</v>
+        <v>0.2045</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0302</v>
+        <v>0.369</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0992</v>
+        <v>-0.1645</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7471</v>
+        <v>3.1243</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8916</v>
+        <v>2.184</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8554</v>
+        <v>0.9402</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0516</v>
+        <v>2.0566</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3058</v>
+        <v>0.3154</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7459</v>
+        <v>1.7412</v>
       </c>
       <c r="J3" t="n">
-        <v>2.056</v>
+        <v>2.0402</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4499</v>
+        <v>1.4369</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0044</v>
+        <v>0.0164</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6708</v>
+        <v>0.0466</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8771</v>
+        <v>0.1925</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2063</v>
+        <v>-0.146</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>I. WASHINGTON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6967</v>
+        <v>0.9749</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4906</v>
+        <v>0.6419</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1873</v>
+        <v>0.3331</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6573</v>
+        <v>0.8051</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2681</v>
+        <v>1.0375</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3892</v>
+        <v>-0.2324</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.8907</v>
+        <v>2.2518</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3228</v>
+        <v>2.8334</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5679</v>
+        <v>-0.5816</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-1.4467</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9453</v>
+        <v>-1.7959</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1787</v>
+        <v>0.3492</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.5878</v>
+        <v>-2.7316</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>1.354</v>
+        <v>0.1487</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8953</v>
+        <v>0.0322</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4588</v>
+        <v>0.1165</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5463</v>
+        <v>0.9317</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5463</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. KOUMADJE</t>
+          <t>D. STEPHENS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0551</v>
+        <v>0.2319</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7594</v>
+        <v>-0.3237</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.7043</v>
+        <v>0.5556</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3391</v>
+        <v>-0.1873</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3971</v>
+        <v>0.5572</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5941</v>
+        <v>-0.0332</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4821</v>
+        <v>0.0862</v>
       </c>
       <c r="L5" t="n">
-        <v>0.112</v>
+        <v>-0.1194</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6521</v>
+        <v>0.4032</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1431</v>
+        <v>-0.2734</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.509</v>
+        <v>0.6766</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0035</v>
+        <v>-0.821</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5243</v>
+        <v>-0.0629</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5208</v>
+        <v>-0.7581</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.571</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8678</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.4387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. WASHINGTON</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0515</v>
+        <v>0.2012</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.223</v>
+        <v>-0.7984</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1715</v>
+        <v>0.9996</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8173</v>
+        <v>-1.6733</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0492</v>
+        <v>-1.283</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2319</v>
+        <v>-0.3903</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2925</v>
+        <v>-0.9305</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8604</v>
+        <v>-0.349</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5679</v>
+        <v>-0.5816</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4752</v>
+        <v>-0.7428</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8112</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.336</v>
+        <v>0.1912</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.722</v>
+        <v>-1.5934</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8934</v>
+        <v>0.8746</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8861</v>
+        <v>0.6361</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0073</v>
+        <v>0.2385</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3722</v>
+        <v>0.1345</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7816</v>
+        <v>-1.1473</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4094</v>
+        <v>1.2819</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.427</v>
+        <v>-3.4208</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0303</v>
+        <v>-2.0251</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3967</v>
+        <v>-1.3957</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.975</v>
+        <v>-2.9939</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.3995</v>
+        <v>-1.4069</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.5754</v>
+        <v>-1.587</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4521</v>
+        <v>-0.427</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2646</v>
+        <v>0.2382</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7652</v>
+        <v>-0.1048</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.343</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. STEPHENS</t>
+          <t>C. KOUMADJE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4367</v>
+        <v>-1.0715</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.881</v>
+        <v>2.533</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4442</v>
+        <v>-3.6045</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3566</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1979</v>
+        <v>1.3384</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5545</v>
+        <v>-0.3853</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0281</v>
+        <v>1.5801</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0866</v>
+        <v>1.4684</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1147</v>
+        <v>0.1117</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3847</v>
+        <v>-0.627</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2844</v>
+        <v>-0.13</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6691</v>
+        <v>-0.497</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4738</v>
+        <v>-0.1416</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6261</v>
+        <v>0.3202</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8478</v>
+        <v>-0.4618</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.5659</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.8603</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8682</v>
+        <v>-1.1556</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2296</v>
+        <v>-1.2285</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3615</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5951</v>
+        <v>-0.5957</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7923</v>
+        <v>-0.7845</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1972</v>
+        <v>0.1888</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1102</v>
+        <v>0.0934</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5306</v>
+        <v>-0.5443</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7053</v>
+        <v>-0.6891</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.433</v>
+        <v>-1.4223</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0465</v>
+        <v>0.7572</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0212</v>
+        <v>0.0439</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0253</v>
+        <v>0.7134</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.16</v>
+        <v>-2.099</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8504</v>
+        <v>-1.8576</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3096</v>
+        <v>-0.2414</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1553</v>
+        <v>-1.1536</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0966</v>
+        <v>-1.0971</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4209</v>
+        <v>-0.4157</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0974</v>
+        <v>-0.0349</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0181</v>
+        <v>0.0185</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3605</v>
+        <v>-2.1106</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9861</v>
+        <v>-3.1228</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6256</v>
+        <v>1.0122</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5898</v>
+        <v>-0.5951</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.098</v>
+        <v>-3.0989</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5082</v>
+        <v>2.5039</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8076</v>
+        <v>0.7659</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0501</v>
+        <v>-1.0729</v>
       </c>
       <c r="L11" t="n">
-        <v>1.8577</v>
+        <v>1.8388</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3974</v>
+        <v>-1.361</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.0479</v>
+        <v>-2.026</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6505</v>
+        <v>0.665</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1829</v>
+        <v>0.0779</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1644</v>
+        <v>-0.2466</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0185</v>
+        <v>0.3245</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8505</v>
+        <v>-3.4327</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.575</v>
+        <v>-3.1787</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2755</v>
+        <v>-0.254</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.925</v>
+        <v>-2.9287</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.173</v>
+        <v>-3.1791</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2479</v>
+        <v>0.2504</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7452</v>
+        <v>-1.7686</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.2276</v>
+        <v>-2.245</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1798</v>
+        <v>-1.1601</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4718</v>
+        <v>-0.0487</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6956</v>
+        <v>-0.272</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2238</v>
+        <v>0.2232</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.773200000000001</v>
+        <v>-0.03140000000000009</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.364700000000001</v>
+        <v>-1.923699999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5914</v>
+        <v>1.892400000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.518</v>
+        <v>-1.5132</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.529199999999999</v>
+        <v>-6.5338</v>
       </c>
       <c r="I13" t="n">
-        <v>5.0113</v>
+        <v>5.020599999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>5.879799999999999</v>
+        <v>5.638500000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>4.028200000000001</v>
+        <v>3.8853</v>
       </c>
       <c r="L13" t="n">
-        <v>1.851600000000001</v>
+        <v>1.7532</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.398</v>
+        <v>-7.1518</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.5574</v>
+        <v>-10.4189</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1595</v>
+        <v>3.2671</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.134</v>
+        <v>-1.138</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7441</v>
+        <v>-14.7961</v>
       </c>
       <c r="R13" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4385000000000001</v>
+        <v>1.3015</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8316000000000001</v>
+        <v>0.9261000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.393</v>
+        <v>0.3753000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>1.317499999999999</v>
+        <v>1.3185</v>
       </c>
       <c r="W13" t="n">
-        <v>6.3312</v>
+        <v>6.307699999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.013500000000001</v>
+        <v>-4.989</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.8917</v>
+        <v>6.2653</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3456</v>
+        <v>3.4231</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5461</v>
+        <v>2.8422</v>
       </c>
       <c r="G14" t="n">
-        <v>3.652</v>
+        <v>3.6575</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8976</v>
+        <v>2.8897</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.7677</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9008</v>
+        <v>3.8697</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6396</v>
+        <v>3.609</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2612</v>
+        <v>0.2607</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2488</v>
+        <v>-0.2122</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.742</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4932</v>
+        <v>0.5071</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0809</v>
+        <v>0.4484</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4476</v>
+        <v>-0.328</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5285</v>
+        <v>0.7765</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9044</v>
+        <v>6.1068</v>
       </c>
       <c r="E15" t="n">
-        <v>5.848</v>
+        <v>5.9169</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0564</v>
+        <v>0.1899</v>
       </c>
       <c r="G15" t="n">
-        <v>4.6614</v>
+        <v>4.6539</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3535</v>
+        <v>1.3501</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3079</v>
+        <v>3.3038</v>
       </c>
       <c r="J15" t="n">
-        <v>5.193</v>
+        <v>5.153</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0638</v>
+        <v>2.0405</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1292</v>
+        <v>3.1126</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5316</v>
+        <v>-0.4992</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7103</v>
+        <v>-0.6904</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0765</v>
+        <v>0.1359</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1693</v>
+        <v>-0.0492</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.1851</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4723</v>
+        <v>2.3733</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2396</v>
+        <v>0.1919</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7118</v>
+        <v>2.1814</v>
       </c>
       <c r="G16" t="n">
-        <v>0.72</v>
+        <v>0.7078</v>
       </c>
       <c r="H16" t="n">
-        <v>3.303</v>
+        <v>3.3002</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.583</v>
+        <v>-2.5923</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1698</v>
+        <v>0.1307</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8328</v>
+        <v>2.8129</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.663</v>
+        <v>-2.6822</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5502</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4701</v>
+        <v>0.4873</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3819</v>
+        <v>-0.4727</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9557</v>
+        <v>-0.4835</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4262</v>
+        <v>0.0108</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1996</v>
+        <v>1.936</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9845</v>
+        <v>2.539</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7848000000000001</v>
+        <v>-0.6029</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9245</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3997</v>
+        <v>0.3992</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5383</v>
+        <v>0.5253</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5874</v>
+        <v>1.5543</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1878</v>
+        <v>1.1754</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3997</v>
+        <v>0.3789</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6494</v>
+        <v>-0.6298</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8726</v>
+        <v>-0.1266</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4688</v>
+        <v>0.1228</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4038</v>
+        <v>-0.2494</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. KRAMPELJ</t>
+          <t>L. PETRASEK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4337</v>
+        <v>-1.9003</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0175</v>
+        <v>-2.3923</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5839</v>
+        <v>0.4919</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2839</v>
+        <v>-2.1106</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.3159</v>
+        <v>1.1367</v>
       </c>
       <c r="I18" t="n">
-        <v>0.032</v>
+        <v>-3.2473</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.3381</v>
+        <v>-0.91</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.701</v>
+        <v>1.31</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6371</v>
+        <v>-2.22</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0542</v>
+        <v>-1.2006</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6149</v>
+        <v>-0.1733</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6691</v>
+        <v>-1.0273</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9429</v>
+        <v>-0.2451</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6816</v>
+        <v>-0.3441</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2613</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9926</v>
+        <v>-2.0576</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1793</v>
+        <v>-0.0643</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1719</v>
+        <v>-1.9934</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0473</v>
+        <v>-1.0446</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5541</v>
+        <v>-0.5516</v>
       </c>
       <c r="I19" t="n">
         <v>-0.4931</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2774</v>
+        <v>-0.287</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3705</v>
+        <v>0.3647</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7699</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3327</v>
+        <v>0.2554</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4567</v>
+        <v>0.2228</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.124</v>
+        <v>0.0327</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. NORMANTAS</t>
+          <t>M. PANTZAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1716</v>
+        <v>-2.2019</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6886</v>
+        <v>-3.7809</v>
       </c>
       <c r="F20" t="n">
-        <v>0.517</v>
+        <v>1.579</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.2625</v>
+        <v>0.4718</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.847</v>
+        <v>0.7608</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4154</v>
+        <v>-0.2889</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.6618</v>
+        <v>0.9698</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3822</v>
+        <v>0.7617</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2796</v>
+        <v>0.2081</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6007</v>
+        <v>-0.4979</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4648</v>
+        <v>-0.0009</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1359</v>
+        <v>-0.497</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5878</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-4.5526</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3424</v>
+        <v>0.1277</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0393</v>
+        <v>-0.3558</v>
       </c>
       <c r="U20" t="n">
-        <v>0.303</v>
+        <v>0.4835</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. PANTZAR</t>
+          <t>M. NORMANTAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2364</v>
+        <v>-2.23</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6242</v>
+        <v>-2.7148</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3878</v>
+        <v>0.4848</v>
       </c>
       <c r="G21" t="n">
-        <v>0.464</v>
+        <v>-4.2622</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7546</v>
+        <v>-2.8408</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2905</v>
+        <v>-1.4214</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9906</v>
+        <v>-2.6864</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7721</v>
+        <v>-1.3897</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2185</v>
+        <v>-1.2967</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5266</v>
+        <v>-1.5758</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0176</v>
+        <v>-1.4511</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.509</v>
+        <v>-0.1246</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.9488</v>
+        <v>1.5934</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.5367</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0877</v>
+        <v>0.281</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2389</v>
+        <v>0.0414</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3266</v>
+        <v>0.2396</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. PETRASEK</t>
+          <t>M. KRAMPELJ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8253</v>
+        <v>-2.7302</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8445</v>
+        <v>-3.2145</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0192</v>
+        <v>0.4842</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1239</v>
+        <v>-2.2817</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1253</v>
+        <v>-2.3177</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.2493</v>
+        <v>0.0359</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8937</v>
+        <v>-2.3546</v>
       </c>
       <c r="K22" t="n">
-        <v>1.3161</v>
+        <v>-1.7139</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.2098</v>
+        <v>-0.6407</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2302</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1908</v>
+        <v>-0.6037</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0395</v>
+        <v>0.6766</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.155</v>
+        <v>0.641</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8166</v>
+        <v>0.506</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3384</v>
+        <v>0.135</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0354</v>
+        <v>-2.9977</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5346</v>
+        <v>-1.7965</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5008</v>
+        <v>-1.2012</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8001</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>2.4127</v>
+        <v>2.4071</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6126</v>
+        <v>-1.6102</v>
       </c>
       <c r="J23" t="n">
-        <v>1.7273</v>
+        <v>1.7125</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4763</v>
+        <v>2.4649</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9272</v>
+        <v>-0.9155</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1379</v>
+        <v>0.1857</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5263</v>
+        <v>0.2925</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3883</v>
+        <v>-0.1067</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.772999999999999</v>
+        <v>2.563699999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5916</v>
+        <v>-1.892399999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>3.364699999999999</v>
+        <v>4.455900000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>1.517900000000001</v>
+        <v>1.5133</v>
       </c>
       <c r="H24" t="n">
-        <v>6.5294</v>
+        <v>6.5337</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.0112</v>
+        <v>-5.0205</v>
       </c>
       <c r="J24" t="n">
-        <v>7.3979</v>
+        <v>7.152000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>10.5575</v>
+        <v>10.4191</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.1594</v>
+        <v>-3.267</v>
       </c>
       <c r="M24" t="n">
-        <v>-5.88</v>
+        <v>-5.6386</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.0282</v>
+        <v>-3.8851</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.8519</v>
+        <v>-1.7535</v>
       </c>
       <c r="P24" t="n">
-        <v>1.134100000000001</v>
+        <v>1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-13.61</v>
+        <v>-13.6579</v>
       </c>
       <c r="R24" t="n">
-        <v>14.744</v>
+        <v>14.796</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4384999999999996</v>
+        <v>1.2307</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3930000000000002</v>
+        <v>-0.3751</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8314999999999998</v>
+        <v>1.6062</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.3176</v>
+        <v>-1.3186</v>
       </c>
       <c r="W24" t="n">
-        <v>5.0135</v>
+        <v>4.988899999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-6.3312</v>
+        <v>-6.307700000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104708_W28.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104708_W28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-4.989</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104708_W28.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-6.307700000000001</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
